--- a/2425def.csv.xlsx
+++ b/2425def.csv.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/28b260e40b8dae5f/Desktop/All new stats data and references/oursafetynet/PBPselfscraped/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/28b260e40b8dae5f/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B68EE304-EE8A-4F19-95BF-44B03BA78E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{84BEE4FD-0CF1-4E86-A6ED-485C5AD1E50E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="20928" windowHeight="12432" xr2:uid="{2D2592E1-9CD0-4441-AE89-A05CB1E7CE04}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="20928" windowHeight="12432" xr2:uid="{5EA32638-1FFB-4F69-A7A1-5143EB1C71DD}"/>
   </bookViews>
   <sheets>
-    <sheet name="csv (98)" sheetId="1" r:id="rId1"/>
+    <sheet name="csv (97)" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -2670,7 +2670,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16FEE1D3-E621-4702-83E7-8E6DC3E9B92E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3D619DB-C079-4376-8BF0-820F4B28ABAA}">
   <dimension ref="A1:I589"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
